--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://73sinfrastructure73strings-my.sharepoint.com/personal/jaikumar_goel_73strings_com/Documents/Desktop/Substitue Management System/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="8_{E37EC00D-1448-8549-9F91-6FD2AB670688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD32DB45-91EC-AD44-94A7-7564E422567B}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="8_{E37EC00D-1448-8549-9F91-6FD2AB670688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E04EBF4C-97A1-2444-B9EE-CE2436765B1F}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="135">
   <si>
     <t>Teacher</t>
   </si>
@@ -375,15 +375,9 @@
     <t>SMT.MANJEET KAUR</t>
   </si>
   <si>
-    <t>SH.SURENDER SHARMA (SKT)</t>
-  </si>
-  <si>
     <t>SMT.PREETI COMP.SCI)</t>
   </si>
   <si>
-    <t>SMT.NEELAM YADAV(FINE ARTS)</t>
-  </si>
-  <si>
     <t>SH.DEVENDER(OSSH)</t>
   </si>
   <si>
@@ -396,15 +390,9 @@
     <t>SH.MANDEEP (PHY. EDU.)</t>
   </si>
   <si>
-    <t>SH.JITENDER BAJAJ(MUSIC)</t>
-  </si>
-  <si>
     <t>SH.SOURABH</t>
   </si>
   <si>
-    <t>SMT.USHA</t>
-  </si>
-  <si>
     <t>SH.Hero Singh</t>
   </si>
   <si>
@@ -420,7 +408,34 @@
     <t>SMT.NANCY</t>
   </si>
   <si>
-    <t>SMT.NEELAM DHANDA(PTA/YOGA)</t>
+    <t>BHUMIKA</t>
+  </si>
+  <si>
+    <t>GARIMA</t>
+  </si>
+  <si>
+    <t>USHA</t>
+  </si>
+  <si>
+    <t>NEHA</t>
+  </si>
+  <si>
+    <t>RIYA</t>
+  </si>
+  <si>
+    <t>SMT.Usha (PTI)</t>
+  </si>
+  <si>
+    <t>SH.JITENDER BAJAJ</t>
+  </si>
+  <si>
+    <t>SMT.NEELAM YADAV</t>
+  </si>
+  <si>
+    <t>SMT.NEELAM DHANDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH.SURENDER SHARMA </t>
   </si>
 </sst>
 </file>
@@ -945,7 +960,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.6640625" customWidth="1"/>
@@ -1905,7 +1920,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="15" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>7</v>
@@ -1926,7 +1941,7 @@
     </row>
     <row r="45" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A45" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>7</v>
@@ -1949,7 +1964,7 @@
     </row>
     <row r="46" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A46" s="15" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>7</v>
@@ -1972,7 +1987,7 @@
     </row>
     <row r="47" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>37</v>
@@ -1995,7 +2010,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="15" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>37</v>
@@ -2018,7 +2033,7 @@
     </row>
     <row r="49" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A49" s="15" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>7</v>
@@ -2041,7 +2056,7 @@
     </row>
     <row r="50" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" s="15" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>7</v>
@@ -2064,7 +2079,7 @@
     </row>
     <row r="51" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A51" s="15" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>7</v>
@@ -2087,7 +2102,7 @@
     </row>
     <row r="52" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="15" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>7</v>
@@ -2110,7 +2125,7 @@
     </row>
     <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="15" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>7</v>
@@ -2133,7 +2148,7 @@
     </row>
     <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>7</v>
@@ -2156,7 +2171,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="15" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>43</v>
@@ -2179,7 +2194,7 @@
     </row>
     <row r="56" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="15" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>30</v>
@@ -2202,7 +2217,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="22" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B57" s="23" t="s">
         <v>23</v>
@@ -2225,10 +2240,14 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="B58" s="25"/>
-      <c r="C58" s="25"/>
+        <v>123</v>
+      </c>
+      <c r="B58" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="26" t="s">
+        <v>7</v>
+      </c>
       <c r="D58" s="26" t="s">
         <v>7</v>
       </c>
@@ -2244,22 +2263,150 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="B59" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E59" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F59" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="G59" s="26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="B60" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E60" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F60" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="G60" s="26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="B61" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F61" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="G61" s="26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="B62" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E62" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F62" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="G62" s="26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="B59" s="25"/>
-      <c r="C59" s="25"/>
-      <c r="D59" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="E59" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F59" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="G59" s="26" t="s">
-        <v>7</v>
-      </c>
+      <c r="B63" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E63" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F63" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="G63" s="26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B64" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E64" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F64" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="G64" s="26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A65" s="25"/>
+      <c r="B65" s="25"/>
+      <c r="C65" s="25"/>
+      <c r="D65" s="25"/>
+      <c r="E65" s="25"/>
+      <c r="F65" s="25"/>
+      <c r="G65" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://73sinfrastructure73strings-my.sharepoint.com/personal/jaikumar_goel_73strings_com/Documents/Desktop/Substitue Management System/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="8_{E37EC00D-1448-8549-9F91-6FD2AB670688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E04EBF4C-97A1-2444-B9EE-CE2436765B1F}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="8_{E37EC00D-1448-8549-9F91-6FD2AB670688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6A84E44-B185-D744-943E-190F22D604FE}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="134">
   <si>
     <t>Teacher</t>
   </si>
@@ -412,9 +412,6 @@
   </si>
   <si>
     <t>GARIMA</t>
-  </si>
-  <si>
-    <t>USHA</t>
   </si>
   <si>
     <t>NEHA</t>
@@ -960,7 +957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.6640625" customWidth="1"/>
@@ -1242,7 +1239,7 @@
         <v>7</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -1324,8 +1321,8 @@
         <v>49</v>
       </c>
       <c r="E16" s="5"/>
-      <c r="G16" s="3" t="s">
-        <v>29</v>
+      <c r="G16" s="6" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.2">
@@ -1920,7 +1917,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>7</v>
@@ -1964,7 +1961,7 @@
     </row>
     <row r="46" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A46" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>7</v>
@@ -2056,7 +2053,7 @@
     </row>
     <row r="50" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>7</v>
@@ -2102,7 +2099,7 @@
     </row>
     <row r="52" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>7</v>
@@ -2148,7 +2145,7 @@
     </row>
     <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>7</v>
@@ -2364,49 +2361,26 @@
         <v>7</v>
       </c>
       <c r="D63" s="26" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E63" s="26" t="s">
         <v>7</v>
       </c>
       <c r="F63" s="26" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="G63" s="26" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A64" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="B64" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D64" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="E64" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F64" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="G64" s="26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A65" s="25"/>
-      <c r="B65" s="25"/>
-      <c r="C65" s="25"/>
-      <c r="D65" s="25"/>
-      <c r="E65" s="25"/>
-      <c r="F65" s="25"/>
-      <c r="G65" s="25"/>
+      <c r="A64" s="25"/>
+      <c r="B64" s="25"/>
+      <c r="C64" s="25"/>
+      <c r="D64" s="25"/>
+      <c r="E64" s="25"/>
+      <c r="F64" s="25"/>
+      <c r="G64" s="25"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://73sinfrastructure73strings-my.sharepoint.com/personal/jaikumar_goel_73strings_com/Documents/Desktop/Substitue Management System/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="8_{E37EC00D-1448-8549-9F91-6FD2AB670688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6A84E44-B185-D744-943E-190F22D604FE}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="8_{E37EC00D-1448-8549-9F91-6FD2AB670688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC17C837-6E07-D94C-9775-4A98FAE2408D}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="135">
   <si>
     <t>Teacher</t>
   </si>
@@ -433,6 +433,9 @@
   </si>
   <si>
     <t xml:space="preserve">SH.SURENDER SHARMA </t>
+  </si>
+  <si>
+    <t>11 ARTS A + F</t>
   </si>
 </sst>
 </file>
@@ -1552,7 +1555,7 @@
         <v>97</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>18</v>
+        <v>134</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>54</v>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://73sinfrastructure73strings-my.sharepoint.com/personal/jaikumar_goel_73strings_com/Documents/Desktop/Substitue Management System/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="8_{E37EC00D-1448-8549-9F91-6FD2AB670688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC17C837-6E07-D94C-9775-4A98FAE2408D}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="8_{E37EC00D-1448-8549-9F91-6FD2AB670688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED3E202F-8607-F140-9FC4-AC52EF7D7E8F}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1558,7 +1558,7 @@
         <v>134</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>36</v>
@@ -1579,7 +1579,7 @@
         <v>29</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="D28" s="14" t="s">
         <v>10</v>
@@ -1588,7 +1588,7 @@
         <v>45</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>7</v>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://73sinfrastructure73strings-my.sharepoint.com/personal/jaikumar_goel_73strings_com/Documents/Desktop/Substitue Management System/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="111" documentId="8_{E37EC00D-1448-8549-9F91-6FD2AB670688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED3E202F-8607-F140-9FC4-AC52EF7D7E8F}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="8_{E37EC00D-1448-8549-9F91-6FD2AB670688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3520691E-EDEA-0D4E-A290-C0433A045A88}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="133">
   <si>
     <t>Teacher</t>
   </si>
@@ -192,18 +192,12 @@
     <t>10TH A</t>
   </si>
   <si>
-    <t>11 ARTS B+C</t>
-  </si>
-  <si>
     <t>9 D</t>
   </si>
   <si>
     <t>9TH B</t>
   </si>
   <si>
-    <t>11  SCI A</t>
-  </si>
-  <si>
     <t>9TH E</t>
   </si>
   <si>
@@ -435,7 +429,7 @@
     <t xml:space="preserve">SH.SURENDER SHARMA </t>
   </si>
   <si>
-    <t>11 ARTS A + F</t>
+    <t>11 ARTS B+F</t>
   </si>
 </sst>
 </file>
@@ -600,14 +594,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -654,6 +647,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -966,50 +965,49 @@
     <col min="1" max="1" width="26.6640625" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.33203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="16.5" customWidth="1"/>
-    <col min="6" max="6" width="22.1640625" customWidth="1"/>
+    <col min="4" max="5" width="21.1640625" customWidth="1"/>
+    <col min="6" max="6" width="37.83203125" customWidth="1"/>
     <col min="7" max="7" width="17.6640625" customWidth="1"/>
     <col min="8" max="8" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="26" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B2" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="27" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="28" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="3" t="s">
@@ -1021,7 +1019,7 @@
     </row>
     <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
@@ -1030,10 +1028,10 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="5" t="s">
         <v>14</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>7</v>
@@ -1044,7 +1042,7 @@
     </row>
     <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>16</v>
@@ -1052,7 +1050,7 @@
       <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -1061,48 +1059,50 @@
       <c r="F4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="F5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>27</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -1111,22 +1111,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="C7" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>7</v>
@@ -1134,19 +1134,19 @@
     </row>
     <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>33</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="9" t="s">
         <v>34</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -1155,9 +1155,9 @@
     </row>
     <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B9" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1169,21 +1169,21 @@
       <c r="E9" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>41</v>
       </c>
       <c r="D10" s="2" t="s">
@@ -1192,7 +1192,7 @@
       <c r="E10" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>43</v>
       </c>
       <c r="G10" s="1" t="s">
@@ -1201,30 +1201,30 @@
     </row>
     <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="5" t="s">
+      <c r="C11" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G11" s="11" t="s">
+      <c r="F11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="10" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
@@ -1232,7 +1232,7 @@
       <c r="C12" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -1241,13 +1241,13 @@
       <c r="F12" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="13" t="s">
-        <v>57</v>
+      <c r="G12" s="12" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>45</v>
@@ -1259,10 +1259,10 @@
         <v>13</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>7</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>42</v>
@@ -1270,13 +1270,13 @@
     </row>
     <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B14" s="3"/>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="9" t="s">
         <v>40</v>
       </c>
       <c r="E14" s="3" t="s">
@@ -1289,7 +1289,7 @@
     </row>
     <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>25</v>
@@ -1297,13 +1297,13 @@
       <c r="C15" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="10" t="s">
         <v>46</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="9" t="s">
         <v>10</v>
       </c>
       <c r="G15" s="3" t="s">
@@ -1312,7 +1312,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
@@ -1323,14 +1323,14 @@
       <c r="D16" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="G16" s="6" t="s">
+      <c r="E16" s="4"/>
+      <c r="G16" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
@@ -1338,34 +1338,34 @@
       <c r="C17" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B18" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>33</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="4" t="s">
         <v>30</v>
       </c>
       <c r="G18" s="3" t="s">
@@ -1374,30 +1374,30 @@
     </row>
     <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="G19" s="11" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>10</v>
@@ -1411,13 +1411,13 @@
       <c r="F20" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>32</v>
@@ -1425,14 +1425,14 @@
       <c r="C21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>37</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>7</v>
@@ -1440,7 +1440,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>42</v>
@@ -1448,7 +1448,7 @@
       <c r="C22" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="9" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="3" t="s">
@@ -1463,12 +1463,13 @@
     </row>
     <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B23" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="1"/>
+      <c r="D23" t="s">
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -1477,24 +1478,24 @@
       <c r="F23" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F24" s="3" t="s">
@@ -1506,12 +1507,12 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="13" t="s">
         <v>40</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -1529,7 +1530,7 @@
     </row>
     <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>8</v>
@@ -1538,24 +1539,24 @@
         <v>7</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>134</v>
+        <v>18</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>7</v>
@@ -1563,9 +1564,11 @@
       <c r="D27" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E27" s="1"/>
+      <c r="E27" s="1" t="s">
+        <v>20</v>
+      </c>
       <c r="F27" s="3" t="s">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>7</v>
@@ -1573,18 +1576,18 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D28" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="D28" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F28" s="3" t="s">
@@ -1596,42 +1599,42 @@
     </row>
     <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="4" t="s">
         <v>27</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G29" s="5" t="s">
+      <c r="E29" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D30" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="13" t="s">
         <v>14</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>57</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>7</v>
@@ -1642,12 +1645,12 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="9" t="s">
         <v>42</v>
       </c>
       <c r="D31" s="2" t="s">
@@ -1665,30 +1668,28 @@
     </row>
     <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="3"/>
+      <c r="D32" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="15" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G32" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>39</v>
@@ -1699,7 +1700,7 @@
       <c r="D33" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F33" s="3" t="s">
@@ -1711,7 +1712,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>15</v>
@@ -1726,15 +1727,15 @@
         <v>7</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>34</v>
@@ -1752,54 +1753,54 @@
         <v>7</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B36" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E36" s="3"/>
-      <c r="F36" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>62</v>
+      <c r="F36" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B37" s="3"/>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E37" s="17" t="s">
+      <c r="E37" s="16" t="s">
         <v>12</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>14</v>
@@ -1808,10 +1809,10 @@
         <v>39</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F38" s="18" t="s">
-        <v>66</v>
+        <v>63</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>64</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>7</v>
@@ -1819,16 +1820,16 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D39" s="12"/>
-      <c r="E39" s="14" t="s">
+      <c r="D39" s="11"/>
+      <c r="E39" s="13" t="s">
         <v>11</v>
       </c>
       <c r="F39" s="3" t="s">
@@ -1840,39 +1841,39 @@
     </row>
     <row r="40" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C40" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D40" s="14" t="s">
+      <c r="D40" s="13" t="s">
         <v>24</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G40" s="5" t="s">
+      <c r="G40" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C41" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D41" s="9"/>
+      <c r="D41" s="8"/>
       <c r="E41" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="F41" s="4" t="s">
         <v>7</v>
       </c>
       <c r="G41" s="3" t="s">
@@ -1881,118 +1882,119 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B42" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="20" t="s">
+      <c r="C42" t="s">
         <v>8</v>
       </c>
+      <c r="D42" s="19"/>
       <c r="E42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G42" s="12"/>
+      <c r="G42" s="11"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" s="15" t="s">
-        <v>133</v>
+      <c r="A44" s="14" t="s">
+        <v>131</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="E45" s="20" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" ht="32" x14ac:dyDescent="0.2">
-      <c r="A45" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D45" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="E45" s="21" t="s">
-        <v>71</v>
-      </c>
       <c r="F45" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="E46" s="20" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" ht="32" x14ac:dyDescent="0.2">
-      <c r="A46" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D46" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="E46" s="21" t="s">
-        <v>71</v>
-      </c>
       <c r="F46" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="15" t="s">
-        <v>115</v>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="14" t="s">
+        <v>113</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D47" s="1" t="s">
@@ -2004,13 +2006,13 @@
       <c r="F47" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G47" s="5" t="s">
-        <v>54</v>
+      <c r="G47" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="15" t="s">
-        <v>116</v>
+      <c r="A48" s="14" t="s">
+        <v>114</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>37</v>
@@ -2031,92 +2033,92 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="32" x14ac:dyDescent="0.2">
-      <c r="A49" s="15" t="s">
-        <v>117</v>
+    <row r="49" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="14" t="s">
+        <v>115</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="E49" s="21" t="s">
-        <v>71</v>
+      <c r="C49" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>69</v>
       </c>
       <c r="F49" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="E50" s="20" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="32" x14ac:dyDescent="0.2">
-      <c r="A50" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D50" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="E50" s="21" t="s">
-        <v>71</v>
-      </c>
       <c r="F50" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="32" x14ac:dyDescent="0.2">
-      <c r="A51" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B51" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D51" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="E51" s="21" t="s">
-        <v>71</v>
+      <c r="D51" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>69</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A52" s="15" t="s">
-        <v>130</v>
+      <c r="A52" s="14" t="s">
+        <v>128</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E52" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F52" s="5" t="s">
+      <c r="E52" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F52" s="4" t="s">
         <v>7</v>
       </c>
       <c r="G52" s="3" t="s">
@@ -2124,10 +2126,10 @@
       </c>
     </row>
     <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A53" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="B53" s="5" t="s">
+      <c r="A53" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="B53" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C53" s="3" t="s">
@@ -2148,7 +2150,7 @@
     </row>
     <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>7</v>
@@ -2156,7 +2158,7 @@
       <c r="C54" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="D54" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E54" s="1" t="s">
@@ -2165,13 +2167,13 @@
       <c r="F54" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G54" s="5" t="s">
+      <c r="G54" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55" s="15" t="s">
-        <v>120</v>
+      <c r="A55" s="14" t="s">
+        <v>118</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>43</v>
@@ -2193,8 +2195,8 @@
       </c>
     </row>
     <row r="56" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A56" s="15" t="s">
-        <v>121</v>
+      <c r="A56" s="14" t="s">
+        <v>119</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>30</v>
@@ -2202,7 +2204,7 @@
       <c r="C56" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D56" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E56" s="1" t="s">
@@ -2211,179 +2213,179 @@
       <c r="F56" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G56" s="5" t="s">
+      <c r="G56" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A57" s="22" t="s">
+      <c r="A57" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="B57" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C57" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E57" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F57" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G57" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="B58" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E58" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F58" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G58" s="25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="B57" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C57" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="D57" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="E57" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="F57" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="G57" s="17" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A58" s="24" t="s">
+      <c r="B59" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E59" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F59" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G59" s="25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="B58" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D58" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="E58" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="G58" s="26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A59" s="24" t="s">
+      <c r="B60" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E60" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F60" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G60" s="25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="B59" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D59" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="E59" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F59" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="G59" s="26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A60" s="24" t="s">
+      <c r="B61" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F61" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G61" s="25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="B60" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D60" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="E60" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="G60" s="26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A61" s="24" t="s">
+      <c r="B62" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E62" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F62" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="G62" s="25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="B61" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D61" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="E61" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F61" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="G61" s="26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A62" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="B62" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D62" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="E62" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="G62" s="26" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A63" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="B63" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D63" s="26" t="s">
+      <c r="B63" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="E63" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F63" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="G63" s="26" t="s">
+      <c r="E63" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F63" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="G63" s="25" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A64" s="25"/>
-      <c r="B64" s="25"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="25"/>
-      <c r="E64" s="25"/>
-      <c r="F64" s="25"/>
-      <c r="G64" s="25"/>
+      <c r="A64" s="24"/>
+      <c r="B64" s="24"/>
+      <c r="C64" s="24"/>
+      <c r="D64" s="24"/>
+      <c r="E64" s="24"/>
+      <c r="F64" s="24"/>
+      <c r="G64" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://73sinfrastructure73strings-my.sharepoint.com/personal/jaikumar_goel_73strings_com/Documents/Desktop/Substitue Management System/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="8_{E37EC00D-1448-8549-9F91-6FD2AB670688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3520691E-EDEA-0D4E-A290-C0433A045A88}"/>
+  <xr:revisionPtr revIDLastSave="169" documentId="8_{E37EC00D-1448-8549-9F91-6FD2AB670688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEA999D5-8DCF-1F43-8BAB-07BD82F5C4EA}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="134">
   <si>
     <t>Teacher</t>
   </si>
@@ -430,6 +430,9 @@
   </si>
   <si>
     <t>11 ARTS B+F</t>
+  </si>
+  <si>
+    <t>SH.Naveen Kumar</t>
   </si>
 </sst>
 </file>
@@ -2379,13 +2382,27 @@
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A64" s="24"/>
-      <c r="B64" s="24"/>
-      <c r="C64" s="24"/>
-      <c r="D64" s="24"/>
-      <c r="E64" s="24"/>
-      <c r="F64" s="24"/>
-      <c r="G64" s="24"/>
+      <c r="A64" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="B64" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E64" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F64" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="G64" s="24" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://73sinfrastructure73strings-my.sharepoint.com/personal/jaikumar_goel_73strings_com/Documents/Desktop/Substitue Management System/public/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rutvi\OneDrive\Desktop\Substitute-Management-System\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="169" documentId="8_{E37EC00D-1448-8549-9F91-6FD2AB670688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEA999D5-8DCF-1F43-8BAB-07BD82F5C4EA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25D8D58-D516-414B-A453-88CDC6F08A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Timetable" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="130">
   <si>
     <t>Teacher</t>
   </si>
@@ -400,18 +400,6 @@
   </si>
   <si>
     <t>SMT.NANCY</t>
-  </si>
-  <si>
-    <t>BHUMIKA</t>
-  </si>
-  <si>
-    <t>GARIMA</t>
-  </si>
-  <si>
-    <t>NEHA</t>
-  </si>
-  <si>
-    <t>RIYA</t>
   </si>
   <si>
     <t>SMT.Usha (PTI)</t>
@@ -962,19 +950,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.6640625" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" customWidth="1"/>
     <col min="3" max="3" width="18.33203125" customWidth="1"/>
-    <col min="4" max="5" width="21.1640625" customWidth="1"/>
-    <col min="6" max="6" width="37.83203125" customWidth="1"/>
+    <col min="4" max="5" width="21.109375" customWidth="1"/>
+    <col min="6" max="6" width="37.77734375" customWidth="1"/>
     <col min="7" max="7" width="17.6640625" customWidth="1"/>
-    <col min="8" max="8" width="23.5" customWidth="1"/>
+    <col min="8" max="8" width="23.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
@@ -997,7 +985,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>70</v>
       </c>
@@ -1020,7 +1008,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>71</v>
       </c>
@@ -1043,7 +1031,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>72</v>
       </c>
@@ -1066,7 +1054,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>73</v>
       </c>
@@ -1089,7 +1077,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>74</v>
       </c>
@@ -1112,7 +1100,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>75</v>
       </c>
@@ -1135,7 +1123,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>76</v>
       </c>
@@ -1156,7 +1144,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>77</v>
       </c>
@@ -1179,7 +1167,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>79</v>
       </c>
@@ -1202,7 +1190,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>78</v>
       </c>
@@ -1225,7 +1213,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>80</v>
       </c>
@@ -1248,7 +1236,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>81</v>
       </c>
@@ -1271,7 +1259,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>82</v>
       </c>
@@ -1290,7 +1278,7 @@
       </c>
       <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>83</v>
       </c>
@@ -1313,7 +1301,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>84</v>
       </c>
@@ -1331,7 +1319,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>85</v>
       </c>
@@ -1354,7 +1342,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>86</v>
       </c>
@@ -1375,7 +1363,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>87</v>
       </c>
@@ -1398,7 +1386,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>88</v>
       </c>
@@ -1418,7 +1406,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>89</v>
       </c>
@@ -1441,7 +1429,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>90</v>
       </c>
@@ -1464,7 +1452,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>91</v>
       </c>
@@ -1485,7 +1473,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>92</v>
       </c>
@@ -1508,7 +1496,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>93</v>
       </c>
@@ -1531,7 +1519,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>94</v>
       </c>
@@ -1554,7 +1542,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>95</v>
       </c>
@@ -1571,13 +1559,13 @@
         <v>20</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>96</v>
       </c>
@@ -1600,7 +1588,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>97</v>
       </c>
@@ -1623,7 +1611,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>98</v>
       </c>
@@ -1646,7 +1634,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>99</v>
       </c>
@@ -1669,7 +1657,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>100</v>
       </c>
@@ -1690,7 +1678,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>101</v>
       </c>
@@ -1713,7 +1701,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>102</v>
       </c>
@@ -1736,7 +1724,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>103</v>
       </c>
@@ -1759,7 +1747,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>104</v>
       </c>
@@ -1780,7 +1768,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>105</v>
       </c>
@@ -1801,7 +1789,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>106</v>
       </c>
@@ -1821,7 +1809,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>107</v>
       </c>
@@ -1842,7 +1830,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>108</v>
       </c>
@@ -1862,7 +1850,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>109</v>
       </c>
@@ -1883,7 +1871,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>110</v>
       </c>
@@ -1902,7 +1890,7 @@
       </c>
       <c r="G42" s="11"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>111</v>
       </c>
@@ -1923,9 +1911,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>7</v>
@@ -1944,7 +1932,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="14" t="s">
         <v>112</v>
       </c>
@@ -1967,9 +1955,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="14" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>7</v>
@@ -1990,7 +1978,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="14" t="s">
         <v>113</v>
       </c>
@@ -2013,7 +2001,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="14" t="s">
         <v>114</v>
       </c>
@@ -2036,7 +2024,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="14" t="s">
         <v>115</v>
       </c>
@@ -2059,9 +2047,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" ht="22.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="14" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>7</v>
@@ -2082,7 +2070,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="14" t="s">
         <v>116</v>
       </c>
@@ -2105,9 +2093,9 @@
         <v>67</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="14" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>7</v>
@@ -2128,7 +2116,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
         <v>117</v>
       </c>
@@ -2151,9 +2139,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>7</v>
@@ -2174,7 +2162,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="14" t="s">
         <v>118</v>
       </c>
@@ -2197,7 +2185,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="14" t="s">
         <v>119</v>
       </c>
@@ -2220,7 +2208,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="21" t="s">
         <v>120</v>
       </c>
@@ -2243,7 +2231,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="23" t="s">
         <v>121</v>
       </c>
@@ -2266,7 +2254,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="23" t="s">
         <v>122</v>
       </c>
@@ -2289,118 +2277,26 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A60" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="B60" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="D60" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E60" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="G60" s="25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A61" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="B61" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="D61" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E61" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F61" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="G61" s="25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A62" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="B62" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="D62" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E62" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="G62" s="25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A63" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="B63" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="D63" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="E63" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F63" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="G63" s="25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A64" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="B64" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="D64" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="E64" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F64" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="G64" s="24" t="s">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B60" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E60" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F60" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="G60" s="24" t="s">
         <v>7</v>
       </c>
     </row>

--- a/public/Substitution_System.xlsx
+++ b/public/Substitution_System.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rutvi\OneDrive\Desktop\Substitute-Management-System\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D25D8D58-D516-414B-A453-88CDC6F08A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B216DCB-1041-4F1F-87EA-CE438129424E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="131">
   <si>
     <t>Teacher</t>
   </si>
@@ -421,6 +421,9 @@
   </si>
   <si>
     <t>SH.Naveen Kumar</t>
+  </si>
+  <si>
+    <t>free</t>
   </si>
 </sst>
 </file>
@@ -1760,7 +1763,9 @@
       <c r="D36" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E36" s="3"/>
+      <c r="E36" s="3" t="s">
+        <v>130</v>
+      </c>
       <c r="F36" s="4" t="s">
         <v>59</v>
       </c>
